--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/oct-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/oct-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC oct-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC oct-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/oct-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/oct-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>77.915.478-5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.092.019-3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>76.504.980-6</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1074,11 @@
           <t>76.217.169-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1383,11 @@
           <t>77.842.230-1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1509,11 @@
           <t>77.842.230-1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1635,11 @@
           <t>77.714.554-1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1761,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1887,11 @@
           <t>77.733.311-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2074,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2139,11 @@
           <t>77.063.770-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2265,11 @@
           <t>77.063.770-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2330,11 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2395,11 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2460,11 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2525,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2466,7 +2542,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>45-371-CM25</t>
+          <t>730566-477-SE25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2491,12 +2567,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,22 +2582,26 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>OG CONSULTORES</t>
+          <t>ADVANSOLUTION TECNOLOGIA LIMITADA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.367.662-5</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>76.005.406-2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>57148.85</v>
+        <v>34642.81</v>
       </c>
     </row>
     <row r="35">
@@ -2697,7 +2777,11 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2710,7 +2794,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2766-1078-CM25</t>
+          <t>4467-9-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2735,12 +2819,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2834,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>76.198.095-5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2849,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>7722.32</v>
+        <v>64792.71</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>45-353-CM25</t>
+          <t>2766-1078-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2791,17 +2875,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,28 +2895,32 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CODER HUB SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.734.221-7</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>46383.83</v>
+        <v>7722.32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4467-9-CM25</t>
+          <t>45-353-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2852,17 +2940,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,28 +2960,32 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
+          <t>CODER HUB SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.198.095-5</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>76.734.221-7</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>64792.71</v>
+        <v>46383.83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1385462-186-CM25</t>
+          <t>45-371-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +3000,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +3010,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +3025,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
+          <t>OG CONSULTORES</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.528.848-7</t>
+          <t>76.367.662-5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +3040,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>26280.97</v>
+        <v>57148.85</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>622844-57-CM25</t>
+          <t>1385462-186-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +3061,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +3071,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +3086,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SECAPPS TECHNOLOGIES SPA</t>
+          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.660.154-3</t>
+          <t>76.528.848-7</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3101,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>31492.27</v>
+        <v>26280.97</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1111089-398-CM25</t>
+          <t>622844-57-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3035,17 +3127,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,28 +3147,32 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>INNOVA TECNOLOGIAS DE LA INFORMACION SPA</t>
+          <t>SECAPPS TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.058.901-2</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>77.660.154-3</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>6734.51</v>
+        <v>31492.27</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>603663-376-CM25</t>
+          <t>1111089-398-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,22 +3187,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3212,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
+          <t>INNOVA TECNOLOGIAS DE LA INFORMACION SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.754.348-2</t>
+          <t>76.058.901-2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3227,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>7304.77</v>
+        <v>6734.51</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3775-897-CM25</t>
+          <t>603663-376-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3157,48 +3253,52 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PAIS DIGITAL SPA</t>
+          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.015.597-5</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>77.754.348-2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>34685.38</v>
+        <v>7304.77</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>603663-378-CM25</t>
+          <t>3775-897-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3218,48 +3318,52 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>PAIS DIGITAL SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>77.015.597-5</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8783.790000000001</v>
+        <v>34685.38</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>603663-377-CM25</t>
+          <t>603663-378-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3299,28 +3403,32 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>OG CONSULTORES</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.367.662-5</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>7328.02</v>
+        <v>8783.790000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4467-11-CM25</t>
+          <t>603663-377-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3340,17 +3448,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3468,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>MAGENTA CONSULTORES LIMITADA</t>
+          <t>OG CONSULTORES</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.018.273-7</t>
+          <t>76.367.662-5</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3483,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>54134.64</v>
+        <v>7328.02</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>895072-133-CM25</t>
+          <t>4467-11-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3401,17 +3509,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.980.540-2</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION PARVULARIA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,28 +3529,32 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>KLEINROCK SPA</t>
+          <t>MAGENTA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.146.212-K</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>76.018.273-7</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>21529.84</v>
+        <v>54134.64</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1067455-173-CM25</t>
+          <t>895072-133-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3462,17 +3574,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>62.000.420-0</t>
+          <t>61.980.540-2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE LA NIÑEZ</t>
+          <t>SUBSECRETARIA DE EDUCACION PARVULARIA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,28 +3594,32 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>KLEINROCK SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>77.146.212-K</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>66369.78999999999</v>
+        <v>21529.84</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>587-603-CM25</t>
+          <t>1067455-173-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3523,17 +3639,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>62.000.420-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUBSECRETARIA DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,28 +3659,32 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CONCORDIA SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.751.321-6</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>9842.209999999999</v>
+        <v>66369.78999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>584105-313-CM25</t>
+          <t>587-603-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3589,12 +3709,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3724,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>CONCORDIA SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>76.751.321-6</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3739,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>382106.17</v>
+        <v>9842.209999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4467-10-CM25</t>
+          <t>584105-313-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3645,17 +3765,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3785,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3800,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>20184.22</v>
+        <v>382106.17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>609-481-CM25</t>
+          <t>4467-10-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,22 +3821,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,28 +3846,32 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>31269.18</v>
+        <v>20184.22</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1388961-427-CM25</t>
+          <t>609-481-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3772,12 +3896,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>65.118.035-K</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,28 +3911,32 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>DATAFY SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.120.292-6</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>37501.83</v>
+        <v>31269.18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1314-43-CM25</t>
+          <t>1388961-427-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,22 +3951,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>65.118.035-K</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,28 +3976,32 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ENVISION INVERSIONES LIMITADA</t>
+          <t>DATAFY SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.693.295-9</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>77.120.292-6</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>62520.65</v>
+        <v>37501.83</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>621923-33-CM25</t>
+          <t>1314-43-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3889,17 +4021,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>53.314.945-6</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +4041,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>ENVISION INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
+          <t>76.693.295-9</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +4056,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>90124.42999999999</v>
+        <v>62520.65</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1725-5758-CM25</t>
+          <t>621923-33-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3955,27 +4087,27 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>53.314.945-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +4117,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>11221.66</v>
+        <v>90124.42999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3181-488-CM25</t>
+          <t>1725-5758-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4138,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,43 +4148,47 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.080.200-7</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>8094.17</v>
+        <v>11221.66</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2305-76-CM25</t>
+          <t>3181-488-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4077,27 +4213,27 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.973.000-3</t>
+          <t>69.080.200-7</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>UNIDAD DE ANALISIS FINANCIERO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>PAULA ALEJANDRA QUITRAL HERRERA, SERVICIOS INFORMATICOS, EMPRESA INDIV</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.092.019-3</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4243,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>28976.74</v>
+        <v>8094.17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2735-1428-CM25</t>
+          <t>2305-76-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4138,12 +4274,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.973.000-3</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>UNIDAD DE ANALISIS FINANCIERO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,28 +4289,32 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ESRI CHILE S A</t>
+          <t>PAULA ALEJANDRA QUITRAL HERRERA, SERVICIOS INFORMATICOS, EMPRESA INDIV</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.504.980-6</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>76.092.019-3</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>37499.79</v>
+        <v>28976.74</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>875-152-CM25</t>
+          <t>2735-1428-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4199,12 +4339,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>60.720.000-9</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,28 +4354,32 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Diseño y Desarrollo Visualmente SpA</t>
+          <t>ESRI CHILE S A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.046.871-1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>76.504.980-6</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>25249.2</v>
+        <v>37499.79</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>895072-173-CM25</t>
+          <t>875-152-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4394,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4404,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.980.540-2</t>
+          <t>60.720.000-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION PARVULARIA</t>
+          <t>AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4419,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>Diseño y Desarrollo Visualmente SpA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.046.871-1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4434,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>17843.96</v>
+        <v>25249.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1191449-102-CM25</t>
+          <t>895072-173-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4321,12 +4465,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>60.905.006-3</t>
+          <t>61.980.540-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SUBSECRETARIA DE EDUCACION PARVULARIA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,28 +4480,32 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>ULLOA Y TORO CONSULTORES ASOCIADOS SPA</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.554.706-7</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>67463.48</v>
+        <v>17843.96</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>624-316-CM25</t>
+          <t>1191449-102-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4382,43 +4530,47 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>60.905.006-3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>ULLOA Y TORO CONSULTORES ASOCIADOS SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>76.554.706-7</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>57729.28</v>
+        <v>67463.48</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>14-568-CM25</t>
+          <t>624-316-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4443,43 +4595,47 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>6782.64</v>
+        <v>57729.28</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2682-413-CM25</t>
+          <t>14-568-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4650,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4660,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.255.500-7</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4675,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Georg</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4690,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>14750.69</v>
+        <v>6782.64</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1314-58-CM25</t>
+          <t>2682-413-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4560,17 +4716,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>69.255.500-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,28 +4736,32 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>AMERICA XXI S.A.</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>78.287.080-7</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>8799.82</v>
+        <v>14750.69</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4294-170-CM25</t>
+          <t>1314-58-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4626,12 +4786,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>65.077.010-2</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4801,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>NETICS SPA</t>
+          <t>AMERICA XXI S.A.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.363.873-1</t>
+          <t>78.287.080-7</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4816,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>8902.17</v>
+        <v>8799.82</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1375757-71-CM25</t>
+          <t>4294-170-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4682,32 +4842,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>65.077.010-2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Andestic SpA</t>
+          <t>NETICS SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.031.392-0</t>
+          <t>76.363.873-1</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4877,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>66030.13</v>
+        <v>8902.17</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1314-57-CM25</t>
+          <t>1375757-71-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4743,32 +4903,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>AMERICA XXI S.A.</t>
+          <t>Andestic SpA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>78.287.080-7</t>
+          <t>76.031.392-0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4938,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>20239.58</v>
+        <v>66030.13</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1111089-453-CM25</t>
+          <t>1314-57-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4959,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4969,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4984,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>COMILLAS SPA</t>
+          <t>AMERICA XXI S.A.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.714.554-1</t>
+          <t>78.287.080-7</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4999,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>41332.83</v>
+        <v>20239.58</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>612-4292-CM25</t>
+          <t>1111089-453-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4865,17 +5025,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,28 +5045,32 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ENVISION INVERSIONES LIMITADA</t>
+          <t>COMILLAS SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.693.295-9</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>77.714.554-1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>164651.19</v>
+        <v>41332.83</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1269832-89-CM25</t>
+          <t>612-4292-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4931,12 +5095,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +5110,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>PAULA ALEJANDRA QUITRAL HERRERA, SERVICIOS INFORMATICOS, EMPRESA INDIV</t>
+          <t>ENVISION INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.092.019-3</t>
+          <t>76.693.295-9</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +5125,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>10092.72</v>
+        <v>164651.19</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1219102-117-CM25</t>
+          <t>1269832-89-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4992,12 +5156,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>62.000.930-k</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Defensoría del Contribuyente</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,28 +5171,32 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ENTELGY CHILE CONSULTORES LIMITADA</t>
+          <t>PAULA ALEJANDRA QUITRAL HERRERA, SERVICIOS INFORMATICOS, EMPRESA INDIV</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.004.023-1</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>76.092.019-3</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>13111.05</v>
+        <v>10092.72</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2434-67-CM25</t>
+          <t>1219102-117-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5048,17 +5216,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>62.000.930-k</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>Defensoría del Contribuyente</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5236,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>ENTELGY CHILE CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>76.004.023-1</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5251,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>62255.97</v>
+        <v>13111.05</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>765-406-CM25</t>
+          <t>2434-67-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5109,48 +5277,52 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.083.021-6</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>14785.64</v>
+        <v>62255.97</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>875-163-CM25</t>
+          <t>765-406-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5175,27 +5347,27 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>60.720.000-9</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>CONSULTORA, CHERRIE PIZARRO SANTOS EMPRESA INDIVIDUAL DE RESPONSABILID</t>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.522.707-0</t>
+          <t>76.083.021-6</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5377,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>17614.23</v>
+        <v>14785.64</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>765-409-CM25</t>
+          <t>875-163-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5398,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,27 +5408,27 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>60.720.000-9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>CONSULTORA, CHERRIE PIZARRO SANTOS EMPRESA INDIVIDUAL DE RESPONSABILID</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.522.707-0</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5438,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>37572.09</v>
+        <v>17614.23</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2307-3666-CM25</t>
+          <t>765-409-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5292,48 +5464,52 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>34816.93</v>
+        <v>37572.09</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>24-1-CM25</t>
+          <t>2307-3666-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5358,27 +5534,27 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SERVICIOS Y COMERCIALIZACIÓN CAIFU SPA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>77.843.971-9</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5564,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>11576.98</v>
+        <v>34816.93</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>885-804-CM25</t>
+          <t>24-1-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5419,12 +5595,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>60.400.000-9</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>CONTRALORIA GENERAL DE LA REPUBLICA</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,28 +5610,32 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>MAGENTA CONSULTORES LIMITADA</t>
+          <t>SERVICIOS Y COMERCIALIZACIÓN CAIFU SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.018.273-7</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
+          <t>77.843.971-9</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>151252.71</v>
+        <v>11576.98</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2298-5153-CM25</t>
+          <t>885-804-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5480,43 +5660,47 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.110.100-2</t>
+          <t>60.400.000-9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
+          <t>CONTRALORIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>MAGENTA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
+          <t>76.018.273-7</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>51564.81</v>
+        <v>151252.71</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>630-310-CM25</t>
+          <t>2298-5153-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,53 +5715,57 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.501.000-6</t>
+          <t>69.110.100-2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL TRABAJO</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>40098.77</v>
+        <v>51564.81</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>45-372-CM25</t>
+          <t>630-310-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5602,12 +5790,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.501.000-6</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DEL TRABAJO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,28 +5805,32 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>INVERSIONES ENVISION CL SPA</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>77.733.311-9</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
+          <t>77.077.350-4</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>29714.89</v>
+        <v>40098.77</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>45-374-CM25</t>
+          <t>45-372-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5678,28 +5870,32 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SOC DE INVESTIGACION Y DESARROLLO KBINNOVA LIMITADA</t>
+          <t>INVERSIONES ENVISION CL SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.098.050-1</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
+          <t>77.733.311-9</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>58752.07</v>
+        <v>29714.89</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5768-149-CM25</t>
+          <t>45-374-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5724,12 +5920,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5935,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>NETICS SPA</t>
+          <t>SOC DE INVESTIGACION Y DESARROLLO KBINNOVA LIMITADA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.363.873-1</t>
+          <t>76.098.050-1</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5950,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>40747.98</v>
+        <v>58752.07</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1605-367-CM25</t>
+          <t>5768-149-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5775,7 +5971,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5785,12 +5981,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>60.803.000-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5996,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>NETICS SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>76.363.873-1</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +6011,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>444468.14</v>
+        <v>40747.98</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>610-96-CM25</t>
+          <t>1057547-34456-SE25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5836,7 +6032,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,43 +6042,47 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.707.000-6</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Energía</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>YOUTOUCH</t>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.605.073-5</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>13551.4</v>
+        <v>46931.4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5768-150-CM25</t>
+          <t>1605-367-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5907,12 +6107,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.803.000-K</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +6122,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>NETICS SPA</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.363.873-1</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,6 +6137,128 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
+        <v>444468.14</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>610-96-CM25</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>61.707.000-6</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Comisión Nacional de Energía</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>YOUTOUCH</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>76.605.073-5</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>13551.4</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>5768-150-CM25</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>NETICS SPA</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>76.363.873-1</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
         <v>39245.51</v>
       </c>
     </row>
